--- a/Assignment 4/Assignmnet 4.xlsx
+++ b/Assignment 4/Assignmnet 4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="199">
   <si>
     <t>feature</t>
   </si>
@@ -586,6 +586,9 @@
   <si>
     <t>The new civil record should not be successfully added 
 to the file and should not appear in the table with the entered phone number</t>
+  </si>
+  <si>
+    <t>Verfiy that the phone number field accepte unique value only</t>
   </si>
   <si>
     <t>Verfiy that the phone number field dosen't accept empty value</t>
@@ -1183,6 +1186,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -1807,146 +1811,149 @@
         <v>124</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>16</v>
@@ -1954,77 +1961,77 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>16</v>
@@ -2032,22 +2039,25 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>16</v>
@@ -2055,71 +2065,71 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>16</v>
@@ -2127,22 +2137,22 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>16</v>
@@ -2150,28 +2160,54 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="H38" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="G39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>